--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008508942972900661</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44143695</v>
+        <v>4020826</v>
       </c>
       <c r="L2" t="n">
-        <v>23631535</v>
+        <v>1761805</v>
       </c>
       <c r="M2" t="n">
-        <v>5555455</v>
+        <v>322774</v>
       </c>
       <c r="N2" t="n">
-        <v>273334</v>
+        <v>7917</v>
       </c>
       <c r="O2" t="n">
-        <v>3221634</v>
+        <v>176945</v>
       </c>
       <c r="P2" t="n">
-        <v>1268921</v>
+        <v>46332</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999880194664001</v>
+        <v>0.9999644160270691</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8459347486495972</v>
+        <v>0.7353276610374451</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7209867835044861</v>
+        <v>0.5480805635452271</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6576507091522217</v>
+        <v>0.4294383227825165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2343989312648773</v>
+        <v>0.04628876969218254</v>
       </c>
       <c r="V2" t="n">
-        <v>0.708033561706543</v>
+        <v>0.4543633759021759</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8073038458824158</v>
+        <v>0.6199836730957031</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002036865544291333</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>44143695</v>
+        <v>4020826</v>
       </c>
       <c r="E3" t="n">
-        <v>6101592</v>
+        <v>938134</v>
       </c>
       <c r="F3" t="n">
-        <v>170604</v>
+        <v>37218</v>
       </c>
       <c r="G3" t="n">
-        <v>19103</v>
+        <v>4099</v>
       </c>
       <c r="H3" t="n">
-        <v>10107</v>
+        <v>2526</v>
       </c>
       <c r="I3" t="n">
-        <v>702</v>
+        <v>150</v>
       </c>
       <c r="J3" t="n">
-        <v>100695438</v>
+        <v>10069394</v>
       </c>
       <c r="K3" t="n">
-        <v>105674497</v>
+        <v>9965762</v>
       </c>
       <c r="L3" t="n">
-        <v>122061559</v>
+        <v>11634920</v>
       </c>
       <c r="M3" t="n">
-        <v>151902555</v>
+        <v>15044631</v>
       </c>
       <c r="N3" t="n">
-        <v>162371880</v>
+        <v>16162904</v>
       </c>
       <c r="O3" t="n">
-        <v>157729938</v>
+        <v>15691572</v>
       </c>
       <c r="P3" t="n">
-        <v>161922507</v>
+        <v>16193796</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8750706911087036</v>
+        <v>0.8036845922470093</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7171215415000916</v>
+        <v>0.5293272733688354</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5931845307350159</v>
+        <v>0.3424570560455322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3052824139595032</v>
+        <v>0.08798817545175552</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6314972043037415</v>
+        <v>0.3456375598907471</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6559042930603027</v>
+        <v>0.2390650361776352</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03212849016620213</v>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>7460661</v>
+        <v>1306683</v>
       </c>
       <c r="E4" t="n">
-        <v>23631535</v>
+        <v>1761805</v>
       </c>
       <c r="F4" t="n">
-        <v>1568640</v>
+        <v>203016</v>
       </c>
       <c r="G4" t="n">
-        <v>120818</v>
+        <v>25250</v>
       </c>
       <c r="H4" t="n">
-        <v>155020</v>
+        <v>28846</v>
       </c>
       <c r="I4" t="n">
-        <v>16609</v>
+        <v>2764</v>
       </c>
       <c r="J4" t="n">
-        <v>762</v>
+        <v>226</v>
       </c>
       <c r="K4" t="n">
-        <v>8039640</v>
+        <v>1447248</v>
       </c>
       <c r="L4" t="n">
-        <v>9145121</v>
+        <v>1452695</v>
       </c>
       <c r="M4" t="n">
-        <v>2891970</v>
+        <v>428845</v>
       </c>
       <c r="N4" t="n">
-        <v>892772</v>
+        <v>163118</v>
       </c>
       <c r="O4" t="n">
-        <v>1328481</v>
+        <v>212490</v>
       </c>
       <c r="P4" t="n">
-        <v>302880</v>
+        <v>28399</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999939799308777</v>
+        <v>0.9999821782112122</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8602561354637146</v>
+        <v>0.7679880857467651</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7190489172935486</v>
+        <v>0.5385407209396362</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6237564086914062</v>
+        <v>0.3810469210147858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2651856541633606</v>
+        <v>0.06066364794969559</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6675788760185242</v>
+        <v>0.3926121890544891</v>
       </c>
       <c r="W4" t="n">
-        <v>0.723771333694458</v>
+        <v>0.3450710475444794</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>412069</v>
+        <v>104830</v>
       </c>
       <c r="E5" t="n">
-        <v>2489869</v>
+        <v>392509</v>
       </c>
       <c r="F5" t="n">
-        <v>5555455</v>
+        <v>322774</v>
       </c>
       <c r="G5" t="n">
-        <v>278076</v>
+        <v>43783</v>
       </c>
       <c r="H5" t="n">
-        <v>567597</v>
+        <v>70263</v>
       </c>
       <c r="I5" t="n">
-        <v>62360</v>
+        <v>8348</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6302168</v>
+        <v>982164</v>
       </c>
       <c r="L5" t="n">
-        <v>9321785</v>
+        <v>1566580</v>
       </c>
       <c r="M5" t="n">
-        <v>3810020</v>
+        <v>619750</v>
       </c>
       <c r="N5" t="n">
-        <v>622014</v>
+        <v>82061</v>
       </c>
       <c r="O5" t="n">
-        <v>1879947</v>
+        <v>334993</v>
       </c>
       <c r="P5" t="n">
-        <v>665692</v>
+        <v>147473</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999953508377075</v>
+        <v>0.9999862313270569</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9126352071762085</v>
+        <v>0.8520094752311707</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8875066637992859</v>
+        <v>0.8160772919654846</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9591740369796753</v>
+        <v>0.9361236095428467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9907724857330322</v>
+        <v>0.9850646257400513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9804554581642151</v>
+        <v>0.9666494131088257</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940998554229736</v>
+        <v>0.9892865419387817</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>132487</v>
+        <v>21236</v>
       </c>
       <c r="E6" t="n">
-        <v>186552</v>
+        <v>26745</v>
       </c>
       <c r="F6" t="n">
-        <v>213147</v>
+        <v>25471</v>
       </c>
       <c r="G6" t="n">
-        <v>273334</v>
+        <v>7917</v>
       </c>
       <c r="H6" t="n">
-        <v>80195</v>
+        <v>7732</v>
       </c>
       <c r="I6" t="n">
-        <v>9520</v>
+        <v>855</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>32971</v>
+        <v>13636</v>
       </c>
       <c r="E7" t="n">
-        <v>336084</v>
+        <v>85531</v>
       </c>
       <c r="F7" t="n">
-        <v>871888</v>
+        <v>144340</v>
       </c>
       <c r="G7" t="n">
-        <v>425108</v>
+        <v>75155</v>
       </c>
       <c r="H7" t="n">
-        <v>3221634</v>
+        <v>176945</v>
       </c>
       <c r="I7" t="n">
-        <v>213689</v>
+        <v>16282</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>1452</v>
+        <v>863</v>
       </c>
       <c r="E8" t="n">
-        <v>31024</v>
+        <v>9776</v>
       </c>
       <c r="F8" t="n">
-        <v>67691</v>
+        <v>18800</v>
       </c>
       <c r="G8" t="n">
-        <v>49667</v>
+        <v>14831</v>
       </c>
       <c r="H8" t="n">
-        <v>515562</v>
+        <v>103123</v>
       </c>
       <c r="I8" t="n">
-        <v>1268921</v>
+        <v>46332</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
